--- a/data/main-source.xlsx
+++ b/data/main-source.xlsx
@@ -141,10 +141,10 @@
     <t>John Carter</t>
   </si>
   <si>
-    <t>206-667-3424</t>
-  </si>
-  <si>
-    <t>1240 W 6th St, Cleveland, OH 44113</t>
+    <t>206-555-0102</t>
+  </si>
+  <si>
+    <t>220 Demo Street, Cleveland, OH 44113</t>
   </si>
   <si>
     <t>Driver 2</t>
@@ -153,10 +153,10 @@
     <t>Maria Lopez</t>
   </si>
   <si>
-    <t>707-773-6386</t>
-  </si>
-  <si>
-    <t>450 N Michigan Ave, Chicago, IL 60611</t>
+    <t>707-555-0100</t>
+  </si>
+  <si>
+    <t>770 Demo Street, Chicago, IL 60611</t>
   </si>
   <si>
     <t>Driver 3</t>
@@ -165,10 +165,10 @@
     <t>Alex Kim</t>
   </si>
   <si>
-    <t>675-486-1335</t>
-  </si>
-  <si>
-    <t>780 Peachtree St, Atlanta, GA 30308</t>
+    <t>675-555-0100</t>
+  </si>
+  <si>
+    <t>960 Demo Street, Atlanta, GA 30308</t>
   </si>
   <si>
     <t>Driver 4</t>
@@ -177,10 +177,10 @@
     <t>Priya Patel</t>
   </si>
   <si>
-    <t>359-469-5960</t>
-  </si>
-  <si>
-    <t>2200 Superior Ave, Cleveland, OH 44114</t>
+    <t>359-555-0100</t>
+  </si>
+  <si>
+    <t>520 Demo Street, Cleveland, OH 44114</t>
   </si>
   <si>
     <t>Driver 5</t>
@@ -189,10 +189,10 @@
     <t>Kenji Tanaka</t>
   </si>
   <si>
-    <t>871-429-6220</t>
-  </si>
-  <si>
-    <t>115 E Broad St, Columbus, OH 43215</t>
+    <t>871-555-0100</t>
+  </si>
+  <si>
+    <t>150 Demo Street, Columbus, OH 43215</t>
   </si>
   <si>
     <t>Driver 6</t>
@@ -201,10 +201,10 @@
     <t>Marcus Chen</t>
   </si>
   <si>
-    <t>283-876-4322</t>
-  </si>
-  <si>
-    <t>500 Pacific Ave, Dallas, TX 75202</t>
+    <t>283-555-0100</t>
+  </si>
+  <si>
+    <t>810 Demo Street, Dallas, TX 75202</t>
   </si>
   <si>
     <t>Driver 7</t>
@@ -213,10 +213,10 @@
     <t>Sofia Gomez</t>
   </si>
   <si>
-    <t>896-828-7164</t>
-  </si>
-  <si>
-    <t>815 Prospect Ave, Cleveland, OH 44115</t>
+    <t>896-555-0100</t>
+  </si>
+  <si>
+    <t>1020 Demo Street, Cleveland, OH 44115</t>
   </si>
   <si>
     <t>Driver 8</t>
@@ -225,10 +225,10 @@
     <t>Liam Smith</t>
   </si>
   <si>
-    <t>820-223-4829</t>
-  </si>
-  <si>
-    <t>240 Madison Ave, Toledo, OH 43604</t>
+    <t>820-555-0100</t>
+  </si>
+  <si>
+    <t>530 Demo Street, Toledo, OH 43604</t>
   </si>
   <si>
     <t>Driver 9</t>
@@ -237,10 +237,10 @@
     <t xml:space="preserve">Emma Brown </t>
   </si>
   <si>
-    <t>206-700-7666</t>
-  </si>
-  <si>
-    <t>330 Civic Center Dr, Columbus, OH 43215</t>
+    <t>206-555-0103</t>
+  </si>
+  <si>
+    <t>630 Demo Street, Columbus, OH 43215</t>
   </si>
   <si>
     <t>Driver 10</t>
@@ -249,10 +249,10 @@
     <t xml:space="preserve">Noah Wilson </t>
   </si>
   <si>
-    <t>582-987-2387</t>
-  </si>
-  <si>
-    <t>110 W Adams St, Chicago, IL 60603</t>
+    <t>582-555-0100</t>
+  </si>
+  <si>
+    <t>130 Demo Street, Chicago, IL 60603</t>
   </si>
   <si>
     <t>Driver 11</t>
@@ -261,10 +261,10 @@
     <t>Olivia Lee</t>
   </si>
   <si>
-    <t>337-857-3607</t>
-  </si>
-  <si>
-    <t>600 Peachtree St, Atlanta, GA 30308</t>
+    <t>337-555-0100</t>
+  </si>
+  <si>
+    <t>900 Demo Street, Atlanta, GA 30308</t>
   </si>
   <si>
     <t>Phone</t>
@@ -282,7 +282,7 @@
     <t>DRV-001</t>
   </si>
   <si>
-    <t>1240 W 6th St, Cleveland, OH</t>
+    <t>220 Demo Street, Cleveland, OH</t>
   </si>
   <si>
     <t>NON-COMPLIANT</t>
@@ -315,13 +315,13 @@
     <t>DRV-002</t>
   </si>
   <si>
-    <t>450 N Michigan Ave, Chicago, IL</t>
+    <t>770 Demo Street, Chicago, IL</t>
   </si>
   <si>
     <t>DRV-003</t>
   </si>
   <si>
-    <t>780 Peachtree St, Atlanta, GA</t>
+    <t>960 Demo Street, Atlanta, GA</t>
   </si>
   <si>
     <t>EXPIRING SOON</t>
@@ -330,13 +330,13 @@
     <t>DRV-004</t>
   </si>
   <si>
-    <t>2200 Superior Ave, Cleveland, OH</t>
+    <t>520 Demo Street, Cleveland, OH</t>
   </si>
   <si>
     <t>DRV-005</t>
   </si>
   <si>
-    <t>115 E Broad St, Columbus, OH</t>
+    <t>150 Demo Street, Columbus, OH</t>
   </si>
   <si>
     <t>VALID</t>
@@ -345,19 +345,19 @@
     <t>DRV-006</t>
   </si>
   <si>
-    <t>500 Pacific Ave, Dallas, TX</t>
+    <t>810 Demo Street, Dallas, TX</t>
   </si>
   <si>
     <t>DRV-007</t>
   </si>
   <si>
-    <t>815 Prospect Ave, Cleveland, OH</t>
+    <t>1020 Demo Street, Cleveland, OH</t>
   </si>
   <si>
     <t>DRV-008</t>
   </si>
   <si>
-    <t>240 Madison Ave, Toledo, OH</t>
+    <t>530 Demo Street, Toledo, OH</t>
   </si>
   <si>
     <t>DRV-009</t>
@@ -366,7 +366,7 @@
     <t>Emma Brown</t>
   </si>
   <si>
-    <t>330 Civic Center Dr, Columbus, OH</t>
+    <t>630 Demo Street, Columbus, OH</t>
   </si>
   <si>
     <t>DRV-010</t>
@@ -375,13 +375,13 @@
     <t>Noah Wilson</t>
   </si>
   <si>
-    <t>110 W Adams St, Chicago, IL</t>
+    <t>130 Demo Street, Chicago, IL</t>
   </si>
   <si>
     <t>DRV-011</t>
   </si>
   <si>
-    <t>600 Peachtree St, Atlanta, GA</t>
+    <t>900 Demo Street, Atlanta, GA</t>
   </si>
   <si>
     <t>DRV-012</t>
@@ -390,10 +390,10 @@
     <t>Robert Johnson</t>
   </si>
   <si>
-    <t>618-623-9317</t>
-  </si>
-  <si>
-    <t>88 S Main St, Akron, OH</t>
+    <t>618-555-0100</t>
+  </si>
+  <si>
+    <t>1040 Demo Street, Akron, OH</t>
   </si>
   <si>
     <t>Asset ID</t>
@@ -1287,7 +1287,7 @@
     <t>/documents/drivers/DRV-011/</t>
   </si>
   <si>
-    <t>88 S Main St, Akron, OH 44308</t>
+    <t>1040 Demo Street, Akron, OH 44308</t>
   </si>
   <si>
     <t>T-106, T-115</t>
